--- a/survey_templates/014_infographic_content_collection_survey--survey_templates.xlsx
+++ b/survey_templates/014_infographic_content_collection_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'informational_graphic'}</t>
+          <t>informational_graphic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Informational Graphic'}</t>
+          <t>Informational Graphic</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'data_visualization'}</t>
+          <t>data_visualization</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Data Visualization'}</t>
+          <t>Data Visualization</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'presentation_graphic'}</t>
+          <t>presentation_graphic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Presentation Graphic'}</t>
+          <t>Presentation Graphic</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'chat_jimmy'}</t>
+          <t>chat_jimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Chat Jimmy'}</t>
+          <t>Chat Jimmy</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
